--- a/linkareer_backend_developer.xlsx
+++ b/linkareer_backend_developer.xlsx
@@ -611,9 +611,7 @@
  [한화시스템 인턴십, 생산마스터 검증 프로세스 구축 : 마스터 데이터 무결성을 확보한 경험]
  이후, 한화시스템 인턴십 과정에서 신규 프로세스 구축을 통해 ‘ABAP 개발’ 역량을 강화하고, 현업의 고질적인 문제를 기술로 직접 해결하는 성과를 이루었습니다. 당시 고객사인 한화케미칼의 생산(PP) 모듈을 분석하던 중, 마스터 데이터 관리가 수기로 이루어져 정합성을 보장하지 못한다는 한계를 발견했습니다. 저는 이를 개선하기 위해 ‘생산 마스터 검증 프로세스 구축’을 주도적으로 제안하고 개발에 착수했습니다.
  우선 Docking Container를 활용해 마스터 정보와 등록 여부를 일괄 검증하는 ALV 기능을 구현하여 데이터 완전성을 높였습니다. 나아가 Hotspot 기능을 적용해 누락된 마스터를 즉시 식별하고 등록 절차를 간소화했습니다. 특히 요약 정보를 시각화 하는 Top-of-Page 로직 구현 단계에서 기술적 난관에 부딪혔으나, 유사 프로그램을 끈질기게 분석하고 선배들과의 협업을 통해 최적의 코드를 완성해 냈 수 있었습니다.
- 이러한 실무 경험을 통해 터득한 ‘비즈니스 설계’와 ‘기술적 구현’ 역량은 고객사의 시스템을 책임지는 단단한 기반이 될 것입니다. 이를 바탕으로 고객사가 기술적 제약 없이 비즈니스 가치 창출에만 몰입할 수 있도록 돕는 지에스아이티엠의 핵심 개발자로서 저의 가치를 증명하겠습니다.
-새창
-목록</t>
+ 이러한 실무 경험을 통해 터득한 ‘비즈니스 설계’와 ‘기술적 구현’ 역량은 고객사의 시스템을 책임지는 단단한 기반이 될 것입니다. 이를 바탕으로 고객사가 기술적 제약 없이 비즈니스 가치 창출에만 몰입할 수 있도록 돕는 지에스아이티엠의 핵심 개발자로서 저의 가치를 증명하겠습니다.</t>
         </is>
       </c>
     </row>
@@ -655,24 +653,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>합격 자소서
-스핀 / 백엔드 개발자 / 2025 하반기
-건국대 / 수학과 / 학점 3.22/4.5 / 토스: 120/IM2 / 한국사검정능력시험: 고급, 컴퓨터활용능력: 1급
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자세히 알아보기
-과학
-교육
-컨설팅
-[자유 양식 자소서]
-■ 지원동기 및 성장 방향
+          <t>■ 지원동기 및 성장 방향
  [성장을 멈추지 않는 문제 해결 중심 개발자]
  저는 현실적인 문제를 해결하며 성취감을 얻고, 그 과정을 통해 지속적으로 성장하는 개발자를 목표로 하고 있습니다. 학부 시절 금융수학과 수학적 모델링, 경제학 과목을 수강하며 논리적 사고력을 키웠고, MATLAB을 통해 처음으로 개발의 매력을 접했습니다. 이후 다양한 직무를 탐색하던 중, 문제 해결과 기술 성장을 동시에 경험할 수 있는 개발자라는 직업에 지원하였습니다.
  이에 Java, Spring Framework, Spring Boot, JSP, MyBatis, Oracle, MySQL, HTML, CSS, JavaScript 등 백엔드 및 웹 개발 핵심 기술을 학습하며 실무 프로젝트 경험을 쌓았습니다. 예를 들어 영화 추천 웹서비스 프로젝트에서는 사용자 행동 데이터 기반 추천 알고리즘을 설계하고, 검색 및 추천 로직의 성능 개선을 주도하며 구조적 문제 해결 역량을 길렀습니다. 또한 Git, Notion, Slack 등 협업 도구를 적극 활용하며 팀원들과의 소통과 일정 관리 능력도 함께 키워왔습니다.
@@ -698,9 +679,7 @@
  두 번의 팀 프로젝트를 진행하며, 첫 프로젝트에서의 문제를 해결하고 이를 다음 프로젝트에 적용한 경험이 있습니다.
  처음에는 UI/UX 논의 부족과 기능 구현 후 디자인을 맞추는 방식으로 인해 CSS 명명 규칙이 불명확해졌고, 웹페이지의 약 40%가 서로 일관되게 연결되지 않아 하나의 통일된 화면으로 보이지 않는 문제가 있었습니다. 또한, 팀원들에게 기능 구현의 자율성을 부여했으나 가이드가 부족해 일정 지연과 기능 미완성이 발생했습니다.
  이를 개선하기 위해, 프로젝트 초기에 UI/UX 회의를 진행하여 CSS 스타일 가이드를 작성하고 디자인을 사전에 확정했습니다. 또한, WBS 기법을 도입하여 작업을 세분화하고 일정 관리를 강화했으며, 애자일 방식을 활용해 우선순위가 높은 기능부터 개발하며 주간 스프린트 점검을 통해 진행 상황을 확인했습니다. 기한 내 구현하지 못한 기능은 회의를 통해 역할을 재조정하여 일정 준수율 95%, 기능 구현 100%를 달성했습니다.
- 협업 강화를 위해 WBS를 Google Drive에 공유해 일정 관리의 투명성을 높였고, Slack을 활용해 오류 발생 시 신속히 의견을 교환하며, Git을 통해 코드 변경 사항을 실시간으로 확인하며 문제 해결 속도를 높였습니다. 이를 통해 불필요한 수정 작업을 줄이고 프로젝트의 일관성을 유지할 수 있었습니다. 결과적으로 협업 프로세스 적용 후 팀원들의 신뢰도와 만족도가 180% 이상 상승했습니다. 이는 팀원들에게 0~10점 만족도 평가를 진행해 수치화한 결과입니다. 회고 시간에 팀원 전원에게 피드백을 받아 수치로 기록했습니다.
-새창
-목록</t>
+ 협업 강화를 위해 WBS를 Google Drive에 공유해 일정 관리의 투명성을 높였고, Slack을 활용해 오류 발생 시 신속히 의견을 교환하며, Git을 통해 코드 변경 사항을 실시간으로 확인하며 문제 해결 속도를 높였습니다. 이를 통해 불필요한 수정 작업을 줄이고 프로젝트의 일관성을 유지할 수 있었습니다. 결과적으로 협업 프로세스 적용 후 팀원들의 신뢰도와 만족도가 180% 이상 상승했습니다. 이는 팀원들에게 0~10점 만족도 평가를 진행해 수치화한 결과입니다. 회고 시간에 팀원 전원에게 피드백을 받아 수치로 기록했습니다.</t>
         </is>
       </c>
     </row>
@@ -910,9 +889,7 @@
         <is>
           <t>- Github : https://github.com/Minjae-An
 - Blog : https://velog.io/@mj3242/posts
-- Linkedin : https://www.linkedin.com/in/minjae-an-1866b4287/
-새창
-목록</t>
+- Linkedin : https://www.linkedin.com/in/minjae-an-1866b4287/</t>
         </is>
       </c>
     </row>
@@ -987,9 +964,7 @@
 당시 Java Spring Boot를 활용해 자사 홈페이지를 관리하는 웹 애플리케이션을 개발하였습니다. 
 기존에 HTML/CSS로 구성된 자사 홈페이지의 정적 페이지에 jQuery를 활용하여 
 Spring Boot 서버로부터 API를 통해 데이터를 가져와 렌더링하도록 구현하였습니다. 
-또한 관리자 페이지의 경우 Bootstrap을 이용하여 직관적인 UI/UX를 제공하도록 개발하였습니다.
-새창
-목록</t>
+또한 관리자 페이지의 경우 Bootstrap을 이용하여 직관적인 UI/UX를 제공하도록 개발하였습니다.</t>
         </is>
       </c>
     </row>
@@ -1085,9 +1060,7 @@
 [SSD 대학원 강의 청강]
 저는 학부연구생으로서 Flash Translation Layer와 이것이 SSD에 미치는 영향을 연구한 경험이 있습니다. 학부 전공과목에서는 SSD에 대해 깊게 공부 할 기회가 없었습니다. 연구실의 지도교수님께서 SSD를 다루는 대학원 강의를 하시는 것을 알게된 저는 해당 대학원 강의를 청강하기로 결심하였습니다. 이를 통해 FTL과 각 정책의 필요성을 배웠습니다. 또한 Wear leveling, Garbage collection 등 여러 정책의 역할과 Mapping 방식에 따른 장단점을 이해 했습니다.
 [SSD 시뮬레이터 분석]
-저는 청강에서 나아가 프로젝트를 해보고 싶어졌습니다. 감사하게도 지도 교수님께서 제 요청을 받아주셨고, 연구실 활동의 일환으로 'SSD 시뮬레이터 분석' 프로젝트를 진행하게 되었습니다. C언어로 구현된 FTL과 SSD 시뮬레이터를 분석하였습니다. FTL 코드와 시뮬레이터를 통해 TC를 기반으로 Read, Write, Garbage collection를 수행하였습니다. 또한 각 동작의 횟수와 소요시간을 측정해 성능을 평가했습니다. Mapping 방식을 바꾸며 IOPS를 측정하는 등 FTL 정책이 SSD의 성능에 미치는 영향을 분석했습니다.
-새창
-목록</t>
+저는 청강에서 나아가 프로젝트를 해보고 싶어졌습니다. 감사하게도 지도 교수님께서 제 요청을 받아주셨고, 연구실 활동의 일환으로 'SSD 시뮬레이터 분석' 프로젝트를 진행하게 되었습니다. C언어로 구현된 FTL과 SSD 시뮬레이터를 분석하였습니다. FTL 코드와 시뮬레이터를 통해 TC를 기반으로 Read, Write, Garbage collection를 수행하였습니다. 또한 각 동작의 횟수와 소요시간을 측정해 성능을 평가했습니다. Mapping 방식을 바꾸며 IOPS를 측정하는 등 FTL 정책이 SSD의 성능에 미치는 영향을 분석했습니다.</t>
         </is>
       </c>
     </row>
@@ -1304,9 +1277,7 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>능동적인 자세로 직무를 수행하는 기업의 일원이 될 수 있다고 생각합니다.
-6개월간 표절검사를 기반으로 다양한 서비스를 제공하는 기업에서 인턴 경험을 하였습니다. 인턴 과정에서 기업 서비스에 대한 아쉬운 점과 개선점에 대해 계속 생각을 하게 되었고 사수와의 대화를 통해 의견을 제시하기도 하였습니다. 이후 기업의 일원이 된다면 적극적으로 업무를 수행하고 의견을 제시하며 모두가 성장하는 기업 문화의 중심에 서고자 하는 목표도 갖게 되었습니다. 개인의 성장과 효율성을 중요시하는 만큼 수동적인 직무 수행은 결과적으로 본인, 기업 모두의 입장에서 효율적이지 못한 과정이라고 생각합니다. 이러한 가치관을 바탕으로 케이아이엔엑스에서 지속적으로 성장하기 위해 노력하며 능동적인 직무 수행을 통해 개인의 성장과 더불어 기업의 발전에도 기여하는 일원이 되고자 노력할 것입니다.
-새창
-목록</t>
+6개월간 표절검사를 기반으로 다양한 서비스를 제공하는 기업에서 인턴 경험을 하였습니다. 인턴 과정에서 기업 서비스에 대한 아쉬운 점과 개선점에 대해 계속 생각을 하게 되었고 사수와의 대화를 통해 의견을 제시하기도 하였습니다. 이후 기업의 일원이 된다면 적극적으로 업무를 수행하고 의견을 제시하며 모두가 성장하는 기업 문화의 중심에 서고자 하는 목표도 갖게 되었습니다. 개인의 성장과 효율성을 중요시하는 만큼 수동적인 직무 수행은 결과적으로 본인, 기업 모두의 입장에서 효율적이지 못한 과정이라고 생각합니다. 이러한 가치관을 바탕으로 케이아이엔엑스에서 지속적으로 성장하기 위해 노력하며 능동적인 직무 수행을 통해 개인의 성장과 더불어 기업의 발전에도 기여하는 일원이 되고자 노력할 것입니다.</t>
         </is>
       </c>
     </row>
@@ -1348,24 +1319,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>합격 자소서
-줌인터넷(ZUM) / 백엔드 개발자 (신입 가능) / 2023 하반기
-한국공학대학교 / 전자공학과 / 학점 3.5/4.5
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자세히 알아보기
-소프트웨어
-교육
-초중고교(K-12)
-[자유 양식]
-"Spring 개발자"
+          <t>"Spring 개발자"
 기존에 학원에서 JSP를 공부한 후, Spring에 적용하기 전에 IT뱅크 학원에서 공부하였습니다. Spring 프로젝트를 진행하면서 여러 예제를 활용하고, 백엔드 외에도 front-end에서의 javascript 활용에 중점을 두고 있습니다. Vanilla JS를 사용하여 프로젝트를 진행하며, document에서의 element 활용과 변수 사용법을 확실히 알아가고 있습니다.
 백엔드에서 필수적인 DB 사용법을 익히기 위해 프로그래머스를 통해 MySql 문제를 해결하고, MS-Sql 프로시저와 쿼리를 사용하여 다양한 데이터를 가공하고 편집했습니다. 현재는 cyberlogitec 회사에서 Oracle을 사용하며, 여러 Toy Project를 MySql, MS-SQL, Oracle 모든 DB를 사용하여 시도해 보았습니다.
 다양한 스크립트 언어와의 경험을 통해 언어 간의 차이점을 이해하고, 각 언어의 장단점을 파악하여 효과적으로 사용할 수 있는 개발자가 되기 위해 노력하고 있습니다.
@@ -1377,9 +1331,7 @@
 "잘 하고, 같이 가는"
 2021년까지 다양한 프로젝트를 시도하며 개발 지식을 쌓았습니다. 2022년에는 JPA 공부에 집중하고, 디프만 참가를 통해 다른 개발자들과 협력하여 프로젝트를 진행해 보았습니다. 그리고 9월까지 클린 코드를 사용한 프로젝트를 완성하고, 이전에 만든 프로젝트를 리팩터링하였습니다.
 이러한 경험을 통해 Spring 개발자로서 한 단계 도약하고, 이후에는 Kotlin을 사용한 프로젝트를 진행하여 더욱 발전하고자 합니다. 이후에는 Kubernetes, Elastic search 등에 대한 공부를 통해 뛰어난 개발자가 되기 위해 노력할 것입니다.
-또한, 뛰어난 개발자로서 다른 사람을 이끌 수 있는 능력을 갖추어 지식 공유와 함께 발전해 나갈 계획입니다.
-새창
-목록</t>
+또한, 뛰어난 개발자로서 다른 사람을 이끌 수 있는 능력을 갖추어 지식 공유와 함께 발전해 나갈 계획입니다.</t>
         </is>
       </c>
     </row>
@@ -1612,9 +1564,7 @@
 다른 사람들이 보기 편한 코드를 만들고 싶습니다.
 제가 맡은 일을 넘어서 함께 일하는 다른 사원들에게도 도움을 줄 수 있을 정도의 실력을 갖추도록 
 꾸준히 공부하고 발전하겠습니다.
-java, jsp, oracle, springboot, mysql, html, css, javascript, jquery
-새창
-목록</t>
+java, jsp, oracle, springboot, mysql, html, css, javascript, jquery</t>
         </is>
       </c>
     </row>
@@ -1754,9 +1704,7 @@
 또한, 완벽주의에서 벗어나는 것도 매우 중요한 경험이었습니다. 예전에는 완벽을 추구하는 것이 중요하다고 생각했지만, 이는 오히려 많은 부담과 스트레스를 안겨주었습니다. 저는 완벽함을 추구하지 않고 자신을 받아들이고, 실패를 통해 더 나은 방향을 찾아나가는 것이 중요하다는 것을 깨달았습니다. 이러한 경험을 통해 자신을 자유롭게 표현하고 자신감을 가질 수 있게 되었고, 다른 사람들에게도 완벽주의에서 벗어나 자신을 받아들이고 삶을 즐기는 방법을 공유하고 싶습니다.
 많이 도전해보고 경험하기, 그리고 완벽주의에서 벗어나기는 제 삶에 큰 변화를 가져다 주었습니다. 이러한 경험들을 다른 사람들과 공유하고 함께 나누면, 더 많은 사람들이 자신의 잠재력을 발견하고 성장할 수 있을 것입니다. 그래서 저는 이 이야기를 다른 사람들에게 꼭 전하고 싶습니다. 많은 도전과 경험을 통해 자신을 발전시키고, 완벽주의에서 벗어나 자유롭게 삶을 즐기는 모습을 보여주기 위해 최선을 다하겠습니다.
 🔥펄어비스 스크랩 TOP 자소서 함께 확인하세요!
-https://linkareer.com/cover-letter/30799
-새창
-목록</t>
+https://linkareer.com/cover-letter/30799</t>
         </is>
       </c>
     </row>
@@ -1798,24 +1746,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>합격 자소서
-애니펜 / AI개발팀, 영상 및 음성 기반 딥러닝 개발자 / 2022 하반기
-전주대 / 무역학과 / 학점 3.98 / X / 사회생활 경험: 가온이앤씨 기획팀 대리 9개월, 데크카본 인사팀 인턴 8개월, 인브리프커뮤니케이션 기획PM 1년 4개월 / 국토교통 데이터활용경진대회 우수상, 3D프린팅 학습데이터 해커톤 최우수상, 딥노이드 노코드경진대회 우수상, 학과 PT 경진대회 우수상, PRE-JOB 채용제안서 경진대회 우수상, 보건복지부 금연서포터즈, 사회혁신센터 요즘것들탐구생활 1차, 사회혁신센터 요즘것들탐구생활 2차, 사회혁신센터 요즘것들탐구생활 3차, 한국생산성본부 신직업메이킹랩, 창업 1회(수익 3000만원) / 기타: MOS Master, ACA Photoshop CS6, ACA illustrator, ACA InDesign CS6, DSAC1 Programmer Certificate, DSAC2 Programmer Certificate
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자세히 알아보기
-프로그래밍
-교육
-머신러닝
-&lt;자유형식 자소서&gt;
-[[실패 속, 개선할 점을 찾아내려는 태도]]
+          <t>[[실패 속, 개선할 점을 찾아내려는 태도]]
 저는 실패 속에서, 낙담이 아닌 개선할 점을 찾습니다.
 실수나 실패를 할 때, 금방 저의 잘못임을 인정하고 성공 케이스와 비교 · 분석을 통해 어떤 부분을 놓치고 있는지 업무를 되돌아보곤 합니다. 진에어 마케팅 아이디어 공모전에서 떨어졌던 경험이 있습니다. 저는 여기서 포기하지 않고 수상작 관련 기사가 나오기만을 기다려, 제 실패의 원인을 파악하였습니다. 그렇게 제 제안은 진에어 기업이 이윤을 창출하는 데에 도움이 될 법한 아이디어가 아니였음을 알 수 있었습니다.
 그 이후부턴 공모전이나 기획 프로젝트에 참가하는 데에 있어, 타겟의 의도를 파악하고 타겟이 원하는 결과물을
@@ -1850,9 +1781,7 @@
 처음에는 개발자를 모아, AI 캐릭터 제작 서비스 아이템을 준비하며 예비창업자가 되어보기도 했습니다.
 여러 지원사업에 선정되기도 하였으나 대표로 발표를 맡게 된 제가 ‘이 아이템에서 사용된 머신러닝 기술’에 대한 답을 할 수 없어 원하던 지원사업에서 혹평을 받게 되며 머신러닝에 대한 갈망은 더 커져갔습니다. 결국 국비지원을 통해 머신러닝을 직접 배웠고, 경영이 아닌 머신러닝이 저의 가장 큰 관심사가 되었습니다.
 저의 기존 경력은 경영부서와 개발자를 이어주는 징검다리로의 역할을 충분히 수행할 수 있을 것입니다.
-더 나아가 프로젝트를 올바른 방향성에 맞춰 기획했던 경험을 살려, 머신러닝 엔지니어로서 탄탄한 기획력과 머신러닝 성과로 최상의 결과를 이끌어 내는 멀티플레이어 역할을 할 자신이 있습니다.
-새창
-목록</t>
+더 나아가 프로젝트를 올바른 방향성에 맞춰 기획했던 경험을 살려, 머신러닝 엔지니어로서 탄탄한 기획력과 머신러닝 성과로 최상의 결과를 이끌어 내는 멀티플레이어 역할을 할 자신이 있습니다.</t>
         </is>
       </c>
     </row>
@@ -2075,9 +2004,7 @@
         <is>
           <t>전공인 전자공학의 지식뿐만 아니라 이전에 공부하였던 기계공학, 정보통신 공학의 지식도 있기에 임베디드 프로그램 설계에 대해서 소프트웨어적인 설계에 대해서 하드웨어의 설계에 대한 이해도를 이용하여 설계 할 수 있다고 생각하여 지원하게 되었습니다.
  어떤 프로그래밍 언어를 알고 있는가는 그리 중요하지 않다고 생각합니다. 중요한 것은 개발자가 프로그래밍 언어에 대한 감각이 얼마나 있는가라고 생각합니다. 집중력과 세심함, 다른 작업자들과의 팀워크 및 커뮤니케이션 능력은 제가 갖추고 있는 역량입니다.
- 입사 이후 1년 안에 회사와 함께 성장하며, 회사와 사용자 Needs에 부응하는 시스템 분석, 자기개발을 게을리 하지 않는 개발자가 되겠습니다.
-새창
-목록</t>
+ 입사 이후 1년 안에 회사와 함께 성장하며, 회사와 사용자 Needs에 부응하는 시스템 분석, 자기개발을 게을리 하지 않는 개발자가 되겠습니다.</t>
         </is>
       </c>
     </row>
@@ -2165,9 +2092,7 @@
         <is>
           <t>저는 전자공학과에서 학습한 하드웨어 지식을 바탕으로, 백엔드 Java 개발에 대한 열정을 키워왔습니다. 학업 중 리눅스 보드와 C언어를 사용한 실습, 라즈베리파이와 아두이노 활용, ATMega 칩 설계 등 다양한 하드웨어 프로젝트를 경험하며 기초를 다졌습니다. 이러한 경험을 통해 하드웨어와 소프트웨어 간의 통신을 이해하고, 이를 실제로 구현하는 능력을 키웠습니다.
 현재는 Spring Boot를 사용한 백엔드 개발에 집중하고 있습니다. JPA, Spring Data JPA, Querydsl을 학습하고, 이를 실제 프로젝트에 적용하여 REST API를 제작하는 등 실무 경험을 쌓았습니다. 특히, Spring Boot와 MySQL을 사용한 동아리 개발 프로젝트를 진행하며, 다양한 사람과 함께 하나의 목표를 이루어 나가는 경험을 얻을 수 있었습니다.
-이러한 경험을 통해 하드웨어와 소프트웨어의 결합, 그리고 백엔드 개발의 중요성을 깊이 이해하게 되었습니다. 전자공학과에서의 배움과 백엔드 개발에 대한 열정을 결합하여, 마켓보로의 식자재 플랫폼 형성에 기여하며 함께 명확한 목표를 완성시키고 싶습니다.
-새창
-목록</t>
+이러한 경험을 통해 하드웨어와 소프트웨어의 결합, 그리고 백엔드 개발의 중요성을 깊이 이해하게 되었습니다. 전자공학과에서의 배움과 백엔드 개발에 대한 열정을 결합하여, 마켓보로의 식자재 플랫폼 형성에 기여하며 함께 명확한 목표를 완성시키고 싶습니다.</t>
         </is>
       </c>
     </row>
@@ -2222,9 +2147,7 @@
 그리고 저희의 상황에 맞추어 내용을 조금씩 변경하고 이에 따른 Trade-off를 살펴 보는 중입니다.
 예를 들어 캐싱 서버를 따로 두는 것은 예산에서 처리하기 힘들 것이라 생각하여 Spring boot 서버에서 Redis를 붙이거나 FK는 ERD상에서는 적용하고 실제로는 제거하는 등의 부분입니다.
 현재는 개발 참여 인원들이 해당 내용에 대해 잘 알지 못하는 상황이라 이전에 내용을 공부한 제가 스터디를 진행하고 있고, 매 주 공부한 내용을 서로 발표하고 토론하고 있습니다.
-이를 통해 기존에 제대로 알고 있다고 생각한 것도 금방 바뀔 수 있다는 것을 알았고, 지금보다 더 열심히 공부하고 새로운 것을 익히고 싶다는 생각을 갖게 되었습니다.
-새창
-목록</t>
+이를 통해 기존에 제대로 알고 있다고 생각한 것도 금방 바뀔 수 있다는 것을 알았고, 지금보다 더 열심히 공부하고 새로운 것을 익히고 싶다는 생각을 갖게 되었습니다.</t>
         </is>
       </c>
     </row>
@@ -2266,20 +2189,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>합격 자소서
-당근페이 / 서버 개발자 인턴 - 당근페이 서비스 (Java / Kotlin) / 2022 상반기
-한국공학대학교 / 전자공학과 / 학점 3.5/4.5
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-[자유양식]
-- **미래를 위한 2022년**
+          <t>- **미래를 위한 2022년**
  - **배움과 기초**
  2021년까지 저는 많은 공부를 한 뒤, 이에 관한 프로젝트를 시도했고 이를 통해 Spring boot에 관한 기본적인 지식을 쌓을 수 있었습니다.
  제가 가장 좋아하는 Spring boot관련 개발 공부 외에도, 알고리즘 풀이를 위해 매일 java를 통한 문제 풀이를 진행하고 있으며, 백엔드에 있어 필수적인 요소 중 하나인 DB공부를 위해 이에 관한 문제 풀이와 기초 공부를 해 왔습니다.
@@ -2319,9 +2229,7 @@
  그렇기 때문에 노력하는 개발자로 남기 위해, 항상 길을 잃지 않고 나아가기 되기 위해 여러 스터디와 프로젝트를 병행하며 개발을 취미로 삼으며 항상 최선을 다하는 저에게 가장 가고싶은 회사로, 매력적으로 다가오게 되었습니다.
  당근마켓에 합류하게 된다면, 저 또한 이곳의 개발자이자 공동체의 일원이 되어 함께 업무를 진행하게 될 것입니다.
  이곳의 철학을 사랑하는 사용자로서, 그리고 모두와 함께 일할 수 있는 공동체의 일원으로서, 회사를 사랑하고 더 나은 사람이 되기 위해 발전하는 노력은 부족함이 없을 것이라 확신할 수 있습니다.
- 지금보다 더욱 열심히 배우려는 자세로 임하고, 스스로를 개발자라고 당당히 소개할 수 있는 사람이 되기 위해 최선을 다하겠습니다.
-새창
-목록</t>
+ 지금보다 더욱 열심히 배우려는 자세로 임하고, 스스로를 개발자라고 당당히 소개할 수 있는 사람이 되기 위해 최선을 다하겠습니다.</t>
         </is>
       </c>
     </row>
@@ -2363,20 +2271,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>합격 자소서
-카카오스타일 / 백엔드 개발자 / 2022 상반기
-한국공학대학교 / 전자공학과 / 학점 3.5/4.5
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-[자유양식]
-- **미래를 위한 도약**
+          <t>- **미래를 위한 도약**
  - **배움과 기초**
  개발자가 되기로 결정한 뒤 저는 많은 공부를 한 뒤, 이에 관한 프로젝트를 시도했고 이를 통해 Spring boot에 관한 기본적인 지식을 쌓을 수 있었습니다.
  제가 가장 좋아하는 Spring boot관련 개발 공부 외에도, java를 통한 알고리즘 문제 풀이를 진행하고 있으며, 백엔드에 있어 필수적인 요소 중 하나인 DB공부를 위해 이에 관한 문제 풀이와 기초 공부를 해 왔습니다.
@@ -2444,9 +2339,7 @@
  4. 가족 여행 등 아무도 해당 도어락을 사용하지 않을 예정일 때에 작동 자체를 막을 수 있도록 하는 기능
  5. 도어락의 개/폐/에러 로그를 저장하여 확인할 수 있도록 하는 기능
  등, 여러 아이디어들이 제안되었으며, 이 중 저희의 기술과 시간 상 구현 가능하다고 판단된 기능을 실제로 완성해 보았고 한이음 프로젝트에 성공적으로 제출할 수 있었습니다.
- 그리고 이런 다양한 아이디어들을 통해 특허를 출원하였으며 생활에 있어 불편한 것이 있다면 이를 해결하기 위한 대응 방안을 생각하는 법을 알 수 있었습니다.
-새창
-목록</t>
+ 그리고 이런 다양한 아이디어들을 통해 특허를 출원하였으며 생활에 있어 불편한 것이 있다면 이를 해결하기 위한 대응 방안을 생각하는 법을 알 수 있었습니다.</t>
         </is>
       </c>
     </row>
@@ -2719,9 +2612,7 @@
 개발 지식들을 저장해두는 블로그입니다.
 날마다 1개의 java알고리즘 문제 풀이를 진행하고 있으며, 이 풀이에 있어 새로운 풀이 방법을 적용해서 진행할 때나, 개인적으로 어렵거나 재미있다고 생각한 문제들을 블로그에서 복기하며 적어두기 위해 시작하였습니다.
 현재는 Git에는 전체적인 flow나 전문적인 내용, 결과 위주로 서술한다면 해당 블로그는 발생했던 문제의 해결 방법이나 세세한 설명 위주로 작성하였습니다.
-이후 현재 진행중인 Spring boot 프로젝트가 완성된다면 해당 프로젝트의 진행 내용들을 이곳에 작성할 예정입니다.
-새창
-목록</t>
+이후 현재 진행중인 Spring boot 프로젝트가 완성된다면 해당 프로젝트의 진행 내용들을 이곳에 작성할 예정입니다.</t>
         </is>
       </c>
     </row>
@@ -2846,9 +2737,7 @@
 이후 ERD 설계및 도메인 작성을 백엔드 개발자들끼리 협업을 통해 진행하였고 저는 쇼핑몰에서 회원이 장바구니에 상품을 담고
 수량 수정 및 삭제하는 기능의 Rest api작성 및 테스트 코드 작성을 담당하였고 성공적으로 마무리 하였습니다.
 이후 프로젝트를 AWS의 Ec2 기능을 통해 배포하였고 Swagger rest api문서 작성을 통해 프론트엔드 개발자분들과 협업하였습니다.
-이 프로젝트를 통해 Query dsl도 사용해보고 여러사람과 협업도 하는 좋은 경험이었습니다.
-새창
-목록</t>
+이 프로젝트를 통해 Query dsl도 사용해보고 여러사람과 협업도 하는 좋은 경험이었습니다.</t>
         </is>
       </c>
     </row>
@@ -3010,9 +2899,7 @@
 어노테이션의 동작원리를 찾아보면서 확인 해본 결과 Mybatis에서 DB에 Query 문을 넘겨줄때 인터셉터가 Query문을 가로채 Rowbounds를 확인해서 있으면 그에 맞는 페이징을 시켜주는 원리로 작동하고 있었습니다.
 그래서 저는 인터셉터에서 제가 작성한 파라미터가 들어오면 들어있는 값을 확인해서 Rowbounds를 객체에 주입시켜서 페이징을 처리할 수 있었습니다.
 처음에는 단순 기존 객체에서 제가 만든 객체로 값을 넘길 때 안 넘겨준 부분에 의해서 발생한 에러라고 생각했지만 아니였고 진짜 원인을 찾는 시간만 하루가 걸리는 문제였으며 해결까지 3일이라는 시간을 투자해서 해결하였습니다.
-이 문제를 해결하면서 어노테이션에 대한 개념 인터셉터에 대한 개념 Paging의 방법 등 다양한 개념을 찾아보고 공부하며 많은 것을 배울 수 있었으며 끝까지 포기하지 않고 원인을 찾아내는 경험을 할 수 있었습니다.
-새창
-목록</t>
+이 문제를 해결하면서 어노테이션에 대한 개념 인터셉터에 대한 개념 Paging의 방법 등 다양한 개념을 찾아보고 공부하며 많은 것을 배울 수 있었으며 끝까지 포기하지 않고 원인을 찾아내는 경험을 할 수 있었습니다.</t>
         </is>
       </c>
     </row>
@@ -3185,9 +3072,7 @@
 처음 회의가 끝난 후 저는 포기할까도 생각했지만 이번에 포기하면 다음에도 포기할 것
 같다는 생각이 들어
 꾸준한 공부를 통해 노력을 했고 그 결과로 프로젝트를 성공한 경험이 가장 보람찬 일이
-었습니다.
-새창
-목록</t>
+었습니다.</t>
         </is>
       </c>
     </row>
@@ -3229,22 +3114,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>합격 자소서
-에프엔에프 / 백엔드개발 / 2021 하반기
-인하대 / 통계 / 학점 3.96/4.5 / 토익: , 토익스피킹: , 오픽: , 기타: / 사회생활 경험: / 한국사검정시험: , 컴퓨터활용능력: , 기타:
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자세히 알아보기
-교육
-전자상거래 서비스
-1.지원동기 및 입사 후 목표에 대해 기재해주세요.
+          <t>1.지원동기 및 입사 후 목표에 대해 기재해주세요.
 [성장하는 E-commerce의 이끌어 나갈 수 있는 트렌드 회사]
 E-commerce 시장이 점점 더 성장하는 가운데 패션과 뷰티에서 부각을 나타내는
 F&amp;F에서 고객들에게 서비스를 제공하는 개발자로 입사하고 싶습니다.
@@ -3297,9 +3167,7 @@
 쇼핑몰 ERD에 심도 있는 이해를 경험하였고 팀 프로젝트를 통해 다른 사람들과
 협업하는 방법에 대해 배울 수 있었습니다.
 위 같은 저만의 강점을 이용해 F&amp;F에 입사하여 고객들에게 좋은 서비스를 개발
-하여 제공하는 F&amp;F의 개발자가 되고 싶습니다.
-새창
-목록</t>
+하여 제공하는 F&amp;F의 개발자가 되고 싶습니다.</t>
         </is>
       </c>
     </row>
@@ -3341,19 +3209,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>합격 자소서
-캐롯손해보험 / 프론트엔드 개발자 / 2021 하반기
-지거국 / 컴퓨터공학 / 학점 3.9 / 토익: 875, 토익스피킹: 130/레벨 6, 오픽: , 기타: / 사회생활 경험: / 한국사검정시험: , 컴퓨터활용능력: , 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-지금까지 자신의 경험 중 혁신적인 성과를 냈다고 자부하는 사례가 있다면 기술하여 주세요.
+          <t>지금까지 자신의 경험 중 혁신적인 성과를 냈다고 자부하는 사례가 있다면 기술하여 주세요.
 “프론트엔드 웹 개발의 첫 도전”
 저는 학부시절 때에는 접해보지 못한 프론트엔드 웹 개발에 기술스택들에 대해 흥미를 가지게 되었고 4학년 여름방학부터 2학기가 진행되는 동안 개인적으로 프로젝트를 만들어가며 공부해나갔습니다. HTML과 CSS를 기본적으로 배운 다음 JavaScript 프레임워크를 이용하는 프로젝트를 만들어보았습니다. 대표적인 JavaScript 프레임워크로 React와 Vue를 골라서 각각 ‘쇼핑몰 사이트’와 ‘영화정보 검색사이트’를 만들었습니다. 성과를 증명해줄 객관적인 수치나 지표가 없긴 하지만 실제로 업무에서 쓰이는 기술로 각각의 기능을 하는 웹사이트를 만들었다는 점에서 스스로 웹 개발 역량이 늘었다고 확신이 들었습니다. 
  React를 활용해서 ‘쇼핑몰 사이트’를 구현하는 과정에서 화면을 구성하는 컴포넌트들은 설계하고 스타일을 입히는 것은 어렵지 않았지만 상품을 장바구니에 추가하고 제거하는 기능을 구현하는 과정에서 어려움이 있었습니다. 기능을 구현하기 위해 React에서 제공하는 useState, useCallback, useMemo 등 여러 Hook과 Context를 사용하는 과정이 익숙하지 않아 시간이 오래 걸리기도 했습니다. 
@@ -3366,9 +3222,7 @@
 입사를 하게 된다면 당사에서 꿈꾸는 Vision에 대해 기술하여 주세요.
  프론트엔드 개발 직무는 고객이 보는 모든 것을 개발하는 직무입니다. 즉 고객이 가장 먼저 보는 부분을 담당하므로 캐롯손해보험의 첫 인상을 만드는 것이라 생각합니다. 저는 이러한 업무가 굉장히 매력적이라 생각하며 고객의 반응을 보고 즉각 반영하는 개발팀에 이바지 할 수 있는 핵심 구성원이 되고 싶습니다. 디바이스와 브라우저는 점점 더 다양해지고 있고 이에 맞는 웹 환경을 고객들에게 제공해주기 위해 저는 프론트엔드 개발자로서 고객과 캐롯손해보험을 이어주는 믿음직한 중간다리 역할을 할 것입니다. 
  프론트엔드 개발 분야는 다른 분야에 비해 트렌드가 빠릅니다. 이에 뒤처지지 않게 저는 하나의 기술을 익혔다고 해서 그 기술에 계속 안주하지 않고 새로운 기술과 트렌드를 꾸준하게 익히도록 노력할 것입니다. 끊임없는 학습을 통해 사용자 인터페이스와 사용자 경험을 기술적으로 정확하게 구현할 수 있도록 항상 노력하고 사용자의 입장에서 생각하겠습니다.
- 저는 앞으로 온라인 비즈니스의 확장이 더 심해질 것이라 생각합니다. 때문에 고객들은 점점 온라인 웹사이트를 점점 많이 접할 것이고 이에 따라 프론트엔드 개발 직무는 비전이 있다고 생각합니다. 새로운 기술을 배우고 익히는 것을 좋아하는 저에게 있어 캐롯손해보험의 프론트엔드 개발 직무는 역량을 발휘하며 함께 성장해나갈 수 있는 가장 적합한 곳이라 확신합니다.
-새창
-목록</t>
+ 저는 앞으로 온라인 비즈니스의 확장이 더 심해질 것이라 생각합니다. 때문에 고객들은 점점 온라인 웹사이트를 점점 많이 접할 것이고 이에 따라 프론트엔드 개발 직무는 비전이 있다고 생각합니다. 새로운 기술을 배우고 익히는 것을 좋아하는 저에게 있어 캐롯손해보험의 프론트엔드 개발 직무는 역량을 발휘하며 함께 성장해나갈 수 있는 가장 적합한 곳이라 확신합니다.</t>
         </is>
       </c>
     </row>
@@ -3419,9 +3273,7 @@
 "항상 기록하고, 새로운 것을 두려워 하지 않는 개발자"
 나날이 발전하는 개발 skill들 속에서 개발자에게 새로운 학습은 필수적입니다. 하지만 유튜브 영상, 논문과 같은 양질의 자료들을 단순히 기억 속에 남기거나, 실습을 한두번 하는 것만으로는 온전히 자기 것으로 만들지 못하고 시간이 지나면 잊혀질 것입니다. 따라서 저는 저의 성장을 기록해 이를 토대로 부족한 점을 피드백 하는 등, 항상 성장하는 개발자를 목표로 하고 있습니다.
 대학생때 프로그래밍에 입문하고서부터 초보적인 부분이라도 제가 짠 코드를 기록하곤 하였습니다. 개발자는 글보다는 코드로 얘기한다고 생각해, 블로그보다는 github를 애용하였습니다. 다양한 알고리즘을 익히기 위해 백준 문제들을 풀고 이를 알고리즘 분류별로 github에 정리해 두곤 했습니다. Spring, Restful api와 같은 웹 백엔드 skill들을 익히고 난 뒤, 이를 활용한 인턴 프로젝트 등 결과물 또한 github에 기록하였습니다. 가끔 이를 되돌아보며 저의 행적에 대한 피드백과 앞으로 어떤 skill을 익혀야 하는지 계획을 수립해 새로운 성장을 도모하고 있습니다.
-지금까지도 여러 코드들을 기록해왔지만, 앞으로는 이론적인 부분 역시 기록할 생각입니다. velog와 같은 블로그에 업무를 통해 배운 이론, 개인적인 공부 등 다양한 글을 올려 후배 개발자들에게 도움이 되고, 선배 개발자들에게 피드백을 받아 모난 부분을 개선할 생각입니다. 이처럼 지식을 기록해 나가면서 선배 개발자 분들처럼 끊임없이 성장하는 개발자가 되고 싶습니다.
-새창
-목록</t>
+지금까지도 여러 코드들을 기록해왔지만, 앞으로는 이론적인 부분 역시 기록할 생각입니다. velog와 같은 블로그에 업무를 통해 배운 이론, 개인적인 공부 등 다양한 글을 올려 후배 개발자들에게 도움이 되고, 선배 개발자들에게 피드백을 받아 모난 부분을 개선할 생각입니다. 이처럼 지식을 기록해 나가면서 선배 개발자 분들처럼 끊임없이 성장하는 개발자가 되고 싶습니다.</t>
         </is>
       </c>
     </row>
@@ -3463,20 +3315,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>합격 자소서
-엠큐닉 / JAVA 개발자 / 2020 하반기
-지거국 / 임베디드 시스템 공학과 / 학점 3.0/4.5 / 오픽: IM2 / 사회생활 경험: 중앙일보 인턴 8개월 / 자율 주행 유모차 논문 발표 동상 수상 / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자유 항목
-[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
+          <t>[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
 학부 시절 8개월 동안 자율 주행 유모차 프로젝트에 참여했습니다. 초기 인식률 50% 미만에서 IR-LOCK 센서를 활용하여 인식률 95% 이상의 성과를 가져온 경험이 있습니다.
 사용자가 착용한 펜던트의 이미지를 IR-LOCK 센서에 저장시켜 유모차의 모터를 구동시켰습니다. 저의 역할은 이미지의 좌표 값을 받아 모터 드라이버로 데이터 값을 parsing하여 전달하는 역할이었습니다.
 프로젝트를 진행하면서 두 가지 문제가 있었습니다. 첫 번째 문제는 사용자가 급하게 몸을 회전할 때, 유모차가 부자연스럽게 상을 쫓아갔습니다. 이를 해결하기 위해 2륜 모터에서 4륜 모터로 교체했습니다. 좌표 데이터 값을 4개의 모터로 전달했으며 부드러운 움직임을 제어할 수 있었습니다. 두 번째 문제는 펜던트 이미지가 갑자기 사라졌을 때, 유모차의 속도 값 제어였습니다. 이를 해결하기 위해 이전의 속도 값을 배열에 저장한 후, 평균값을 구해 서서히 정지시켰습니다.
@@ -3494,9 +3333,7 @@
 첫째, 기존 중앙일보의 디지털 스페셜 페이지의 문제점을 파악하고 보완했습니다. 기존 서비스의 문제점은 해상도 변화에 이미지 깨짐 현상과 Javascript 함수 초기화의 부재였습니다. 예외적인 비율을 갖고 있는 모바일 기기에서 이미지 깨짐 현상이 있었습니다. 기기마다 다른 해상도를 적용시키기 위해 Media Query를 사용했고, 디자이너에게 받은 이미지 파일을 요소 별로 분리했습니다. 동적 움직임이 필요한 이미지를 분리한 뒤, Position 값의 변화와 Css Animation 함수를 사용해 다양한 해상도 값에서도 부드러운 움직임을 소화 시킬 수 있게 되었습니다.
 또한 Javascript 초기화 함수가 작성이 되어있지 않았습니다. 데이터가 중복되는 현상이 발생하고, Animation 함수의 메모리 사용량이 비정상적으로 높았습니다. 이를 해결하기 위해 초기화 버튼의 생성과 일정 스크롤의 값을 벗어나면 데이터를 초기화 시켰습니다. Animation 함수의 메모리 사용량을 줄이기 위해 무한 Loop를 사용하던 함수를 Count를 통해 수정했습니다.
 둘째, 하루에 30분씩 한 팀을 이루었던 기자, 기획자, 디자이너와 개발 상황을 공유하는 시간을 가지며 아이디어를 소통했습니다. 다소 지루할 수 있는 미세먼지의 정보를 효율적으로 전달하기 위해 적절한 애니메이션을 기획하는 데 중점을 맞추었고, 개발자로서는 함수 초기화를 통해 다양한 애니메이션을 구현해 내는 데 힘썼습니다.
-이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.
-새창
-목록</t>
+이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.</t>
         </is>
       </c>
     </row>
@@ -3538,20 +3375,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>합격 자소서
-씨인플러스 / Java 개발자 / 2020 하반기
-지거국 / 임베디드 시스템 공학과 / 학점 3.0/4.5 / 오픽: IM2 / 사회생활 경험: 중앙일보 인턴 8개월 / 자율 주행 유모차 논문 발표 동상 수상 / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자유 항목
-[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
+          <t>[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
 학부 시절 8개월 동안 자율 주행 유모차 프로젝트에 참여했습니다. 초기 인식률 50% 미만에서 IR-LOCK 센서를 활용하여 인식률 95% 이상의 성과를 가져온 경험이 있습니다.
 사용자가 착용한 펜던트의 이미지를 IR-LOCK 센서에 저장시켜 유모차의 모터를 구동시켰습니다. 저의 역할은 이미지의 좌표 값을 받아 모터 드라이버로 데이터 값을 parsing하여 전달하는 역할이었습니다.
 프로젝트를 진행하면서 두 가지 문제가 있었습니다. 첫 번째 문제는 사용자가 급하게 몸을 회전할 때, 유모차가 부자연스럽게 상을 쫓아갔습니다. 이를 해결하기 위해 2륜 모터에서 4륜 모터로 교체했습니다. 좌표 데이터 값을 4개의 모터로 전달했으며 부드러운 움직임을 제어할 수 있었습니다. 두 번째 문제는 펜던트 이미지가 갑자기 사라졌을 때, 유모차의 속도 값 제어였습니다. 이를 해결하기 위해 이전의 속도 값을 배열에 저장한 후, 평균값을 구해 서서히 정지시켰습니다.
@@ -3569,9 +3393,7 @@
 첫째, 기존 중앙일보의 디지털 스페셜 페이지의 문제점을 파악하고 보완했습니다. 기존 서비스의 문제점은 해상도 변화에 이미지 깨짐 현상과 Javascript 함수 초기화의 부재였습니다. 예외적인 비율을 갖고 있는 모바일 기기에서 이미지 깨짐 현상이 있었습니다. 기기마다 다른 해상도를 적용시키기 위해 Media Query를 사용했고, 디자이너에게 받은 이미지 파일을 요소 별로 분리했습니다. 동적 움직임이 필요한 이미지를 분리한 뒤, Position 값의 변화와 Css Animation 함수를 사용해 다양한 해상도 값에서도 부드러운 움직임을 소화 시킬 수 있게 되었습니다.
 또한 Javascript 초기화 함수가 작성이 되어있지 않았습니다. 데이터가 중복되는 현상이 발생하고, Animation 함수의 메모리 사용량이 비정상적으로 높았습니다. 이를 해결하기 위해 초기화 버튼의 생성과 일정 스크롤의 값을 벗어나면 데이터를 초기화 시켰습니다. Animation 함수의 메모리 사용량을 줄이기 위해 무한 Loop를 사용하던 함수를 Count를 통해 수정했습니다.
 둘째, 하루에 30분씩 한 팀을 이루었던 기자, 기획자, 디자이너와 개발 상황을 공유하는 시간을 가지며 아이디어를 소통했습니다. 다소 지루할 수 있는 미세먼지의 정보를 효율적으로 전달하기 위해 적절한 애니메이션을 기획하는 데 중점을 맞추었고, 개발자로서는 함수 초기화를 통해 다양한 애니메이션을 구현해 내는 데 힘썼습니다.
-이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.
-새창
-목록</t>
+이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.</t>
         </is>
       </c>
     </row>
@@ -3613,20 +3435,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>합격 자소서
-와이비에스 / Web 및 Java 개발자 / 2020 하반기
-지거국 / 임베디드 시스템 공학과 / 학점 3.0/4.5 / 오픽: IM2 / 사회생활 경험: 중앙일보 인턴 8개월 / 자율 주행 유모차 논문 발표 동상 수상 / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자유 항목
-[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
+          <t>[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
 학부 시절 8개월 동안 자율 주행 유모차 프로젝트에 참여했습니다. 초기 인식률 50% 미만에서 IR-LOCK 센서를 활용하여 인식률 95% 이상의 성과를 가져온 경험이 있습니다.
 사용자가 착용한 펜던트의 이미지를 IR-LOCK 센서에 저장시켜 유모차의 모터를 구동시켰습니다. 저의 역할은 이미지의 좌표 값을 받아 모터 드라이버로 데이터 값을 parsing하여 전달하는 역할이었습니다.
 프로젝트를 진행하면서 두 가지 문제가 있었습니다. 첫 번째 문제는 사용자가 급하게 몸을 회전할 때, 유모차가 부자연스럽게 상을 쫓아갔습니다. 이를 해결하기 위해 2륜 모터에서 4륜 모터로 교체했습니다. 좌표 데이터 값을 4개의 모터로 전달했으며 부드러운 움직임을 제어할 수 있었습니다. 두 번째 문제는 펜던트 이미지가 갑자기 사라졌을 때, 유모차의 속도 값 제어였습니다. 이를 해결하기 위해 이전의 속도 값을 배열에 저장한 후, 평균값을 구해 서서히 정지시켰습니다.
@@ -3644,9 +3453,7 @@
 첫째, 기존 중앙일보의 디지털 스페셜 페이지의 문제점을 파악하고 보완했습니다. 기존 서비스의 문제점은 해상도 변화에 이미지 깨짐 현상과 Javascript 함수 초기화의 부재였습니다. 예외적인 비율을 갖고 있는 모바일 기기에서 이미지 깨짐 현상이 있었습니다. 기기마다 다른 해상도를 적용시키기 위해 Media Query를 사용했고, 디자이너에게 받은 이미지 파일을 요소 별로 분리했습니다. 동적 움직임이 필요한 이미지를 분리한 뒤, Position 값의 변화와 Css Animation 함수를 사용해 다양한 해상도 값에서도 부드러운 움직임을 소화 시킬 수 있게 되었습니다.
 또한 Javascript 초기화 함수가 작성이 되어있지 않았습니다. 데이터가 중복되는 현상이 발생하고, Animation 함수의 메모리 사용량이 비정상적으로 높았습니다. 이를 해결하기 위해 초기화 버튼의 생성과 일정 스크롤의 값을 벗어나면 데이터를 초기화 시켰습니다. Animation 함수의 메모리 사용량을 줄이기 위해 무한 Loop를 사용하던 함수를 Count를 통해 수정했습니다.
 둘째, 하루에 30분씩 한 팀을 이루었던 기자, 기획자, 디자이너와 개발 상황을 공유하는 시간을 가지며 아이디어를 소통했습니다. 다소 지루할 수 있는 미세먼지의 정보를 효율적으로 전달하기 위해 적절한 애니메이션을 기획하는 데 중점을 맞추었고, 개발자로서는 함수 초기화를 통해 다양한 애니메이션을 구현해 내는 데 힘썼습니다.
-이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.
-새창
-목록</t>
+이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.</t>
         </is>
       </c>
     </row>
@@ -3688,19 +3495,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>합격 자소서
-이베이코리아 / SW 개발자 / 2020 하반기
-지거국 / 임베디드 시스템 공학과 / 학점 3.0/4.5 / 오픽: IM2 / 사회생활 경험: 중앙일보 인턴 8개월 / 자율 주행 유모차 논문 발표 동상 수상 / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-본인의 강점과 역량을 잘 볼 수 있도록 표현해주세요.
+          <t>본인의 강점과 역량을 잘 볼 수 있도록 표현해주세요.
 본인에 대해 자세히 소개하여 주십시오 (지원동기, 직무경험, 장단점 등) (최소 100자, 최대 1,000자 입력가능)
 이베이 코리아의 Front 개발 직무에 참여하고 싶어 지원했습니다. 대한민국 최대 규모의 e-commerce 산업 시장에 일조하는 개발자가 되고 싶습니다. 검열에 사용되는 AI 기술 및 할인 행사에 사용되는 소비 패턴에 따른 광고 노출 기술 등 최신 트렌드에 맞는 개발을 하고 싶습니다. 기본을 중요시하고 최신 트렌드를 추구하는 저의 성향은 이베이 코리아에서 근무하기 적합하다고 판단하여 지원했습니다.
 저의 전공은 임베디드 시스템입니다. 주로 HW와 관련된 수업을 수강하고 프로젝트를 진행했습니다. 하지만 Java 과목을 수강한 후, 애플리케이션 개발에 관심을 갖게 되었습니다. 이에 졸업 후, 애플리케이션 개발자가 되기 위해 단계적으로 저의 역량을 상승시키기 위해 노력했습니다.
@@ -3709,9 +3504,7 @@
 [신규 서비스 Front 개발, 일평균 PV 30% 증가]
 8개월 동안 중앙일보에서 신규 서비스인 먼지알지의 모바일 웹 Front 개발을 진행했습니다. 기자, 기획자, 디자이너와 한 팀을 이루어 디지털 스페셜 페이지 콘텐츠를 제작했습니다. Javascript와 CSS를 사용해 Front 개발을 진행했습니다. 주 2회 아이디어 회의를 통해 콘텐츠를 설정했습니다. 댓글과 게시판의 유저 피드백을 바탕으로 수정 작업을 진행하는 등의 신규 유저 확보에 온 힘을 기울였습니다. 결국 초기 목표인 기존 서비스의 일평균 1500PV 보다 30% 높은 일평균 2000PV를 유지할 수 있었습니다.
  본인이 보유한 Skill 들의 활용 정도를 0(없음)~5(마스터) 기준으로 작성해주세요. [작성예시 : ① Java - 5 ② C - 4 ③ Python- 4 등] (최대 1,000자 입력가능)
-① Java – 3 ② C – 3 ③ HTML – 4 ④ Javascript – 4 ⑤ Css – 4 ⑥ Spring – 1 ⑦ Ajax – 2 ⑧ JSON – 2 ⑨ Oracle – 2 ⑩ Mybatis – 1 ⑪ Media query - 3
-새창
-목록</t>
+① Java – 3 ② C – 3 ③ HTML – 4 ④ Javascript – 4 ⑤ Css – 4 ⑥ Spring – 1 ⑦ Ajax – 2 ⑧ JSON – 2 ⑨ Oracle – 2 ⑩ Mybatis – 1 ⑪ Media query - 3</t>
         </is>
       </c>
     </row>
@@ -3753,20 +3546,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>합격 자소서
-오아시스마켓 / 개발자 / 2020 하반기
-지거국 / 임베디드 시스템 공학과 / 학점 3.0/4.5 / 오픽: IM2 / 사회생활 경험: 중앙일보 인턴 8개월 / 자율 주행 유모차 논문 발표 동상 수상 / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자유 항목
-[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
+          <t>[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
 학부 시절 8개월 동안 자율 주행 유모차 프로젝트에 참여했습니다. 초기 인식률 50% 미만에서 IR-LOCK 센서를 활용하여 인식률 95% 이상의 성과를 가져온 경험이 있습니다.
 사용자가 착용한 펜던트의 이미지를 IR-LOCK 센서에 저장시켜 유모차의 모터를 구동시켰습니다. 저의 역할은 이미지의 좌표 값을 받아 모터 드라이버로 데이터 값을 parsing하여 전달하는 역할이었습니다.
 프로젝트를 진행하면서 두 가지 문제가 있었습니다. 첫 번째 문제는 사용자가 급하게 몸을 회전할 때, 유모차가 부자연스럽게 상을 쫓아갔습니다. 이를 해결하기 위해 2륜 모터에서 4륜 모터로 교체했습니다. 좌표 데이터 값을 4개의 모터로 전달했으며 부드러운 움직임을 제어할 수 있었습니다. 두 번째 문제는 펜던트 이미지가 갑자기 사라졌을 때, 유모차의 속도 값 제어였습니다. 이를 해결하기 위해 이전의 속도 값을 배열에 저장한 후, 평균값을 구해 서서히 정지시켰습니다.
@@ -3784,9 +3564,7 @@
 첫째, 기존 중앙일보의 디지털 스페셜 페이지의 문제점을 파악하고 보완했습니다. 기존 서비스의 문제점은 해상도 변화에 이미지 깨짐 현상과 Javascript 함수 초기화의 부재였습니다. 예외적인 비율을 갖고 있는 모바일 기기에서 이미지 깨짐 현상이 있었습니다. 기기마다 다른 해상도를 적용시키기 위해 Media Query를 사용했고, 디자이너에게 받은 이미지 파일을 요소 별로 분리했습니다. 동적 움직임이 필요한 이미지를 분리한 뒤, Position 값의 변화와 Css Animation 함수를 사용해 다양한 해상도 값에서도 부드러운 움직임을 소화 시킬 수 있게 되었습니다.
 또한 Javascript 초기화 함수가 작성이 되어있지 않았습니다. 데이터가 중복되는 현상이 발생하고, Animation 함수의 메모리 사용량이 비정상적으로 높았습니다. 이를 해결하기 위해 초기화 버튼의 생성과 일정 스크롤의 값을 벗어나면 데이터를 초기화 시켰습니다. Animation 함수의 메모리 사용량을 줄이기 위해 무한 Loop를 사용하던 함수를 Count를 통해 수정했습니다.
 둘째, 하루에 30분씩 한 팀을 이루었던 기자, 기획자, 디자이너와 개발 상황을 공유하는 시간을 가지며 아이디어를 소통했습니다. 다소 지루할 수 있는 미세먼지의 정보를 효율적으로 전달하기 위해 적절한 애니메이션을 기획하는 데 중점을 맞추었고, 개발자로서는 함수 초기화를 통해 다양한 애니메이션을 구현해 내는 데 힘썼습니다.
-이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.
-새창
-목록</t>
+이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.</t>
         </is>
       </c>
     </row>
@@ -3828,20 +3606,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>합격 자소서
-인라이플 / JAVA 개발자 / 2020 하반기
-지거국 / 임베디드 시스템 공학과 / 학점 3.0/4.5 / 오픽: IM2 / 사회생활 경험: 중앙일보 인턴 8개월 / 자율 주행 유모차 논문 발표 동상 수상 / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자유 항목
-[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
+          <t>[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
 학부 시절 8개월 동안 자율 주행 유모차 프로젝트에 참여했습니다. 초기 인식률 50% 미만에서 IR-LOCK 센서를 활용하여 인식률 95% 이상의 성과를 가져온 경험이 있습니다.
 사용자가 착용한 펜던트의 이미지를 IR-LOCK 센서에 저장시켜 유모차의 모터를 구동시켰습니다. 저의 역할은 이미지의 좌표 값을 받아 모터 드라이버로 데이터 값을 parsing하여 전달하는 역할이었습니다.
 프로젝트를 진행하면서 두 가지 문제가 있었습니다. 첫 번째 문제는 사용자가 급하게 몸을 회전할 때, 유모차가 부자연스럽게 상을 쫓아갔습니다. 이를 해결하기 위해 2륜 모터에서 4륜 모터로 교체했습니다. 좌표 데이터 값을 4개의 모터로 전달했으며 부드러운 움직임을 제어할 수 있었습니다. 두 번째 문제는 펜던트 이미지가 갑자기 사라졌을 때, 유모차의 속도 값 제어였습니다. 이를 해결하기 위해 이전의 속도 값을 배열에 저장한 후, 평균값을 구해 서서히 정지시켰습니다.
@@ -3859,9 +3624,7 @@
 첫째, 기존 중앙일보의 디지털 스페셜 페이지의 문제점을 파악하고 보완했습니다. 기존 서비스의 문제점은 해상도 변화에 이미지 깨짐 현상과 Javascript 함수 초기화의 부재였습니다. 예외적인 비율을 갖고 있는 모바일 기기에서 이미지 깨짐 현상이 있었습니다. 기기마다 다른 해상도를 적용시키기 위해 Media Query를 사용했고, 디자이너에게 받은 이미지 파일을 요소 별로 분리했습니다. 동적 움직임이 필요한 이미지를 분리한 뒤, Position 값의 변화와 Css Animation 함수를 사용해 다양한 해상도 값에서도 부드러운 움직임을 소화 시킬 수 있게 되었습니다.
 또한 Javascript 초기화 함수가 작성이 되어있지 않았습니다. 데이터가 중복되는 현상이 발생하고, Animation 함수의 메모리 사용량이 비정상적으로 높았습니다. 이를 해결하기 위해 초기화 버튼의 생성과 일정 스크롤의 값을 벗어나면 데이터를 초기화 시켰습니다. Animation 함수의 메모리 사용량을 줄이기 위해 무한 Loop를 사용하던 함수를 Count를 통해 수정했습니다.
 둘째, 하루에 30분씩 한 팀을 이루었던 기자, 기획자, 디자이너와 개발 상황을 공유하는 시간을 가지며 아이디어를 소통했습니다. 다소 지루할 수 있는 미세먼지의 정보를 효율적으로 전달하기 위해 적절한 애니메이션을 기획하는 데 중점을 맞추었고, 개발자로서는 함수 초기화를 통해 다양한 애니메이션을 구현해 내는 데 힘썼습니다.
-이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.
-새창
-목록</t>
+이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.</t>
         </is>
       </c>
     </row>
@@ -3903,20 +3666,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>합격 자소서
-공게임즈 / 웹 개발자 / 2020 하반기
-지거국 / 임베디드 시스템 공학과 / 학점 3.0/4.5 / 오픽: IM2 / 사회생활 경험: 중앙일보 인턴 8개월 / 자율 주행 유모차 논문 발표 동상 수상 / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자유 항목
-[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
+          <t>[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
 학부 시절 8개월 동안 자율 주행 유모차 프로젝트에 참여했습니다. 초기 인식률 50% 미만에서 IR-LOCK 센서를 활용하여 인식률 95% 이상의 성과를 가져온 경험이 있습니다.
 사용자가 착용한 펜던트의 이미지를 IR-LOCK 센서에 저장시켜 유모차의 모터를 구동시켰습니다. 저의 역할은 이미지의 좌표 값을 받아 모터 드라이버로 데이터 값을 parsing하여 전달하는 역할이었습니다.
 프로젝트를 진행하면서 두 가지 문제가 있었습니다. 첫 번째 문제는 사용자가 급하게 몸을 회전할 때, 유모차가 부자연스럽게 상을 쫓아갔습니다. 이를 해결하기 위해 2륜 모터에서 4륜 모터로 교체했습니다. 좌표 데이터 값을 4개의 모터로 전달했으며 부드러운 움직임을 제어할 수 있었습니다. 두 번째 문제는 펜던트 이미지가 갑자기 사라졌을 때, 유모차의 속도 값 제어였습니다. 이를 해결하기 위해 이전의 속도 값을 배열에 저장한 후, 평균값을 구해 서서히 정지시켰습니다.
@@ -3934,9 +3684,7 @@
 첫째, 기존 중앙일보의 디지털 스페셜 페이지의 문제점을 파악하고 보완했습니다. 기존 서비스의 문제점은 해상도 변화에 이미지 깨짐 현상과 Javascript 함수 초기화의 부재였습니다. 예외적인 비율을 갖고 있는 모바일 기기에서 이미지 깨짐 현상이 있었습니다. 기기마다 다른 해상도를 적용시키기 위해 Media Query를 사용했고, 디자이너에게 받은 이미지 파일을 요소 별로 분리했습니다. 동적 움직임이 필요한 이미지를 분리한 뒤, Position 값의 변화와 Css Animation 함수를 사용해 다양한 해상도 값에서도 부드러운 움직임을 소화 시킬 수 있게 되었습니다.
 또한 Javascript 초기화 함수가 작성이 되어있지 않았습니다. 데이터가 중복되는 현상이 발생하고, Animation 함수의 메모리 사용량이 비정상적으로 높았습니다. 이를 해결하기 위해 초기화 버튼의 생성과 일정 스크롤의 값을 벗어나면 데이터를 초기화 시켰습니다. Animation 함수의 메모리 사용량을 줄이기 위해 무한 Loop를 사용하던 함수를 Count를 통해 수정했습니다.
 둘째, 하루에 30분씩 한 팀을 이루었던 기자, 기획자, 디자이너와 개발 상황을 공유하는 시간을 가지며 아이디어를 소통했습니다. 다소 지루할 수 있는 미세먼지의 정보를 효율적으로 전달하기 위해 적절한 애니메이션을 기획하는 데 중점을 맞추었고, 개발자로서는 함수 초기화를 통해 다양한 애니메이션을 구현해 내는 데 힘썼습니다.
-이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.
-새창
-목록</t>
+이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.</t>
         </is>
       </c>
     </row>
@@ -3978,19 +3726,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>합격 자소서
-다날 / 신입 개발자 / 2020 하반기
-강남대 / 컴퓨터학과 / 학점 2.89 / 토익스피킹: 110/5, 오픽: IL / 사회생활 경험: N tech Service / 2개월 / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-본인이 생각하는 좋은 회사의 조건을 우선 순위로 나열하고, 그 이유를 알려주세요.(300자 이상) -
+          <t>본인이 생각하는 좋은 회사의 조건을 우선 순위로 나열하고, 그 이유를 알려주세요.(300자 이상) -
 [성장기회, 복지, 협동력]
  가장 좋은 회사의 조건은 성장기회, 복지, 협동력을 가진 회사입니다.
  먼저 성장기회를 얻는다는 것은 개인의 성장을 통해 회사에 발전을 이바지해 자아실현을 할 수 있기 때문입니다. 일하며 개인의 능력치를 키울 수 있고, 공동의 목표를 가지고 성취감을 느낄 수 있는 곳이 회사라고 생각합니다. 그래서 자기계발과 일을 하며 성장할 수 있는 회사가 첫 번째 좋은 회사의 조건입니다.
@@ -4019,9 +3755,7 @@
  QA 인턴을 하면서 로드테스트 및 테스트 자동화를 했던 경험이 있습니다. 평소 테스트는 개발의 연장선이라 생각하고 QA 직무에 도전했습니다. JUnit를 이용한 단위테스트를 경험해보고 '클린코드'라는 책을 통해서 테스트에 대한 간단한 지식을 가지고 있는 정도였습니다. 그리고 인턴 기간 동안 버전에 따른 테스트 방법, 테스트 케이스 산출, 버그 리포팅, 테스트 자동화, 실전 테스트 경험을 쌓을 수 있었습니다.
  하지만 실제 QA 직무의 테스트는 생각했던 테스트와 달랐습니다. 효율적이고 체계화된 테스트 작업을 꿈꿨던 것에 반해 너무나 반복적인 테스트 작업으로 지루하고 답답했습니다. 지루하고 반복적인 작업에서 테스트의 본질을 잊고 좁은 시야로 테스트를 진행했습니다. 이외에 웹과 모바일 버전 세팅의 어려움과 알지 못했던 Python을 활용한 테스트로 인해 어려움을 겪었습니다.
  이 문제들을 타개하기 위해서 반복적인 테스트 작업을 Selenium을 사용해 테스트 자동화를 하고 효율적인 테스트케이스를 찾기 위해 PairWise, 탐색적 테스팅 기법과 같은 다양한 테스트 기법을 공부했습니다. 하지만 자주 변하는 서비스를 맡아서 테스트 자동화를 만드는 것이 효과적으로 쓰이지 않을 수 있었습니다. 그럼에도 불구하고 저는 테스트자동화를 시스템화와 모듈화를 통해 자동화를 만든다면 후에 쓰일 것으로 판단하고 테스트 자동화를 만들었습니다.
- 인턴이 끝나고 테스트에 대해서 알 수 있었습니다. 효율적인 테스트 방법에 대해서 공부했고 이를 활용해 개발하는 커리어나 넓은 범위의 IT를 쌓을 수 있었습니다. QA 경험을 통해서 개발에 대한 넓은 시야를 가질 수 있는 계기였습니다.
-새창
-목록</t>
+ 인턴이 끝나고 테스트에 대해서 알 수 있었습니다. 효율적인 테스트 방법에 대해서 공부했고 이를 활용해 개발하는 커리어나 넓은 범위의 IT를 쌓을 수 있었습니다. QA 경험을 통해서 개발에 대한 넓은 시야를 가질 수 있는 계기였습니다.</t>
         </is>
       </c>
     </row>
@@ -4063,26 +3797,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>합격 자소서
-이베이코리아 / 개발자 / 2020 하반기
-성균관대 / 글로벌경제학 / 학점 3.9 / 토익: 945 / 사회생활 경험: 티몬 인턴 6개월 / 경기도블록체인해커톤 1위, KISA 블록체인 그랜드챌린지 2위
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자세히 알아보기
-과학
-컨설팅
-교육 자료
-교육
-본인의 강점과 역량을 잘 볼 수 있도록 표현해주세요.
-본인에 대해 자세히 소개하여 주십시오 (지원동기, 직무경험, 장단점 등) (최소 100자, 최대 1,000자 입력가능)
-## 직무경험: 티몬 FIT개발팀 소속 데이터분석 인턴
+          <t>## 직무경험: 티몬 FIT개발팀 소속 데이터분석 인턴
 개발팀 소속이지만, 여행사업부의 기획팀에 파견되어 근무했습니다. 앱과 웹의 구글 애널리틱스 세션 데이터를 대시보드로 시각화하고, 기획팀과 개발팀이 원활히 소통할 수 있도록 중개하는 업무를 담당했습니다. 예컨대 PC웹 페이지 개편 과정에서 기획팀이 원하는 영역의 이벤트 트래킹이 가능하도록 개발팀과 협의하고, 기획팀의 요구조건을 개발팀이 실행할 수 있도록 문서화하는 작업을 수행했습니다.
 ## 한줄소개: 끊임없이 도전하고, 빠르게 습득하며, 가치를 성과로 증명하는 루키
 저는 새로운 지식을 배우고, 사용자에게 가치를 제공하는 방법을 찾기 위해 적극적으로 도전하는 사람입니다.
@@ -4098,9 +3813,7 @@
 Java - 3. 언어의 특징을 이해하고, 스프링 프레임워크를 활용한 웹서비스 개발 가능
 Java Springboot과 JPA, Java Security를 활용한 REST API 개발.
 JavaScript, Go - 2. 공식 문서를 보고, 개발에 필요한 기능을 구현할 수 있음
-블록체인 프레임워크 Hyperledger Fabric에서 스마트 컨트랙트 구현
-새창
-목록</t>
+블록체인 프레임워크 Hyperledger Fabric에서 스마트 컨트랙트 구현</t>
         </is>
       </c>
     </row>
@@ -4142,20 +3855,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>합격 자소서
-오로스테크놀로지 / Software개발자 / 2020 하반기
-인천대학교 / 전자공학과 / 학점 3.52/4.5 / 토익: 860, 오픽: IM1, 기타: JLPT N4 / 교내대회 우수상 / 컴퓨터활용능력: 1급
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-입사 후 포부
-저는 한 사람의 SW개발자로서 크게 두 가지의 목표를 설정하고 싶습니다. 첫째로는 제 손을 거친 Software가 자사 제품에 적용되는 보람을 느끼고 싶습니다. 또 효율적인 데이터 분석 툴 설계에 도움을 주는 사람이 되기 위해 끊임없이 고민하고 노력하겠습니다. 두 번째는 좋은 엔지니어를 양성하고 후배들에게 존경받을 수 있는 엔지니어가 되겠습니다. 팀 전체가 성장할 수 있도록 많은 도움을 주며 좋은 엔지니어를 양성하고 싶습니다. 이 두 가지 목표를 달성하기 위해서 비트교육센터에서 진행하는 SW 관련 교육을 게을리하지 않고 항상 누군가에게 도움을 줄 수 있는 사원이 되도록 끊임없이 도전하고 성장하겠습니다.
+          <t>저는 한 사람의 SW개발자로서 크게 두 가지의 목표를 설정하고 싶습니다. 첫째로는 제 손을 거친 Software가 자사 제품에 적용되는 보람을 느끼고 싶습니다. 또 효율적인 데이터 분석 툴 설계에 도움을 주는 사람이 되기 위해 끊임없이 고민하고 노력하겠습니다. 두 번째는 좋은 엔지니어를 양성하고 후배들에게 존경받을 수 있는 엔지니어가 되겠습니다. 팀 전체가 성장할 수 있도록 많은 도움을 주며 좋은 엔지니어를 양성하고 싶습니다. 이 두 가지 목표를 달성하기 위해서 비트교육센터에서 진행하는 SW 관련 교육을 게을리하지 않고 항상 누군가에게 도움을 줄 수 있는 사원이 되도록 끊임없이 도전하고 성장하겠습니다.
 지원 동기
 “함께 발전하는 기업”
 회사를 선택할 때 고려할 요소가 많지만 제가 생각할 때 가장 중요한 요소는 그 회사에서 얼마나 성장하고 발전
@@ -4177,9 +3877,7 @@
 “Object Detection Robot”
 저희 작품은 Machine Learning 프로그램을 활용해 무선으로 움직이는 AI 로봇이 실시간 스트리밍 되는 
 영상정보를 받아 물체를 인식해 사용자에게 정보를 제공해주는 작품이었습니다. 스트리밍 중인 영상에서 실시간으로 물체를 인식해야 하므로 최대한 빠른 속도로 인식할 수 있는 알고리즘이 필요했고, YOLO-v3 알고리즘을 선택하게 되었습니다. 하지만 코드 속의 각 함수들의 역할을 무엇인지, 어떤 순서로 알고리즘이 형성되어 있는지 이해하기 어려웠습니다. 그래서 코드 해석에 무엇 보다 많은 비중을 두며 어떤 함수를 수정하면 어떤 기능을 제어 할 수 있는지 이해하는데 공을 들였습니다. 코드속의 함수들을 이해하고 원하는 기능을 위해 조금씩 수정하여 수많은 테스트를 거쳤습니다. 이러한 과정을 통해 작품을 완성하고, 우수작품으로 선정되어 캡스톤디자인부문 우수상을 받았습니다. 이 프로젝트를 통해 소프트웨어 및 하드웨어 플랫폼 개발역량과 더불어 
-Machine learning 프로그램 활용 역량과 관련 지식을 쌓을 수 있었습니다.
-새창
-목록</t>
+Machine learning 프로그램 활용 역량과 관련 지식을 쌓을 수 있었습니다.</t>
         </is>
       </c>
     </row>
@@ -4221,24 +3919,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>합격 자소서
-인솔라인 / 대중교통(모빌리티) 플랫폼 백엔드 개발 / 2020 상반기
-지거국 / 임베디드 시스템 공학과 / 학점 3.0/4.5 / 오픽: IM2 / 사회생활 경험: 중앙일보 인턴 8개월 / 자율 주행 유모차 논문 발표 동상 수상 / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자세히 알아보기
-과학
-컴퓨터 하드웨어
-교육 자료
-자유 항목
-[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
+          <t>[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
 학부 시절 8개월 동안 자율 주행 유모차 프로젝트에 참여했습니다. 초기 인식률 50% 미만에서 IR-LOCK 센서를 활용하여 인식률 95% 이상의 성과를 가져온 경험이 있습니다.
 사용자가 착용한 펜던트의 이미지를 IR-LOCK 센서에 저장시켜 유모차의 모터를 구동시켰습니다. 저의 역할은 이미지의 좌표 값을 받아 모터 드라이버로 데이터 값을 parsing하여 전달하는 역할이었습니다.
 프로젝트를 진행하면서 두 가지 문제가 있었습니다. 첫 번째 문제는 사용자가 급하게 몸을 회전할 때, 유모차가 부자연스럽게 상을 쫓아갔습니다. 이를 해결하기 위해 2륜 모터에서 4륜 모터로 교체했습니다. 좌표 데이터 값을 4개의 모터로 전달했으며 부드러운 움직임을 제어할 수 있었습니다. 두 번째 문제는 펜던트 이미지가 갑자기 사라졌을 때, 유모차의 속도 값 제어였습니다. 이를 해결하기 위해 이전의 속도 값을 배열에 저장한 후, 평균값을 구해 서서히 정지시켰습니다.
@@ -4256,9 +3937,7 @@
 첫째, 기존 중앙일보의 디지털 스페셜 페이지의 문제점을 파악하고 보완했습니다. 기존 서비스의 문제점은 해상도 변화에 이미지 깨짐 현상과 Javascript 함수 초기화의 부재였습니다. 예외적인 비율을 갖고 있는 모바일 기기에서 이미지 깨짐 현상이 있었습니다. 기기마다 다른 해상도를 적용시키기 위해 Media Query를 사용했고, 디자이너에게 받은 이미지 파일을 요소 별로 분리했습니다. 동적 움직임이 필요한 이미지를 분리한 뒤, Position 값의 변화와 Css Animation 함수를 사용해 다양한 해상도 값에서도 부드러운 움직임을 소화 시킬 수 있게 되었습니다.
 또한 Javascript 초기화 함수가 작성이 되어있지 않았습니다. 데이터가 중복되는 현상이 발생하고, Animation 함수의 메모리 사용량이 비정상적으로 높았습니다. 이를 해결하기 위해 초기화 버튼의 생성과 일정 스크롤의 값을 벗어나면 데이터를 초기화 시켰습니다. Animation 함수의 메모리 사용량을 줄이기 위해 무한 Loop를 사용하던 함수를 Count를 통해 수정했습니다.
 둘째, 하루에 30분씩 한 팀을 이루었던 기자, 기획자, 디자이너와 개발 상황을 공유하는 시간을 가지며 아이디어를 소통했습니다. 다소 지루할 수 있는 미세먼지의 정보를 효율적으로 전달하기 위해 적절한 애니메이션을 기획하는 데 중점을 맞추었고, 개발자로서는 함수 초기화를 통해 다양한 애니메이션을 구현해 내는 데 힘썼습니다.
-이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.
-새창
-목록</t>
+이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.</t>
         </is>
       </c>
     </row>
@@ -4300,20 +3979,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>합격 자소서
-노아에이티에스 / 개발자(금융시스템 개발) / 2020 상반기
-지거국 / 임베디드 시스템 공학과 / 학점 3.0/4.5 / 오픽: IM2 / 사회생활 경험: 중앙일보 인턴 8개월 / 자율 주행 유모차 논문 발표 동상 수상 / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-자유 항목
-[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
+          <t>[인식률 50% -&gt; 95%, IR-LOCK 센서를 활용한 자율 주행 유모차]
 학부 시절 8개월 동안 자율 주행 유모차 프로젝트에 참여했습니다. 초기 인식률 50% 미만에서 IR-LOCK 센서를 활용하여 인식률 95% 이상의 성과를 가져온 경험이 있습니다.
 사용자가 착용한 펜던트의 이미지를 IR-LOCK 센서에 저장시켜 유모차의 모터를 구동시켰습니다. 저의 역할은 이미지의 좌표 값을 받아 모터 드라이버로 데이터 값을 parsing하여 전달하는 역할이었습니다.
 프로젝트를 진행하면서 두 가지 문제가 있었습니다. 첫 번째 문제는 사용자가 급하게 몸을 회전할 때, 유모차가 부자연스럽게 상을 쫓아갔습니다. 이를 해결하기 위해 2륜 모터에서 4륜 모터로 교체했습니다. 좌표 데이터 값을 4개의 모터로 전달했으며 부드러운 움직임을 제어할 수 있었습니다. 두 번째 문제는 펜던트 이미지가 갑자기 사라졌을 때, 유모차의 속도 값 제어였습니다. 이를 해결하기 위해 이전의 속도 값을 배열에 저장한 후, 평균값을 구해 서서히 정지시켰습니다.
@@ -4331,9 +3997,7 @@
 첫째, 기존 중앙일보의 디지털 스페셜 페이지의 문제점을 파악하고 보완했습니다. 기존 서비스의 문제점은 해상도 변화에 이미지 깨짐 현상과 Javascript 함수 초기화의 부재였습니다. 예외적인 비율을 갖고 있는 모바일 기기에서 이미지 깨짐 현상이 있었습니다. 기기마다 다른 해상도를 적용시키기 위해 Media Query를 사용했고, 디자이너에게 받은 이미지 파일을 요소 별로 분리했습니다. 동적 움직임이 필요한 이미지를 분리한 뒤, Position 값의 변화와 Css Animation 함수를 사용해 다양한 해상도 값에서도 부드러운 움직임을 소화 시킬 수 있게 되었습니다.
 또한 Javascript 초기화 함수가 작성이 되어있지 않았습니다. 데이터가 중복되는 현상이 발생하고, Animation 함수의 메모리 사용량이 비정상적으로 높았습니다. 이를 해결하기 위해 초기화 버튼의 생성과 일정 스크롤의 값을 벗어나면 데이터를 초기화 시켰습니다. Animation 함수의 메모리 사용량을 줄이기 위해 무한 Loop를 사용하던 함수를 Count를 통해 수정했습니다.
 둘째, 하루에 30분씩 한 팀을 이루었던 기자, 기획자, 디자이너와 개발 상황을 공유하는 시간을 가지며 아이디어를 소통했습니다. 다소 지루할 수 있는 미세먼지의 정보를 효율적으로 전달하기 위해 적절한 애니메이션을 기획하는 데 중점을 맞추었고, 개발자로서는 함수 초기화를 통해 다양한 애니메이션을 구현해 내는 데 힘썼습니다.
-이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.
-새창
-목록</t>
+이러한 노력 때문인지 목표했던 2000PV 달성과 함께 일일 최대 25000PV의 성과를 얻을 수 있었습니다. 앞으로도 신규 서비스를 출시하며 배운 서비스의 개발과정을 통해 빠르게 적응하며, 협업의 자세를 실천하여 높은 성과를 달성하는 개발자가 되겠습니다.</t>
         </is>
       </c>
     </row>
@@ -4375,19 +4039,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>합격 자소서
-위메프 / 개발자 / 2020 상반기
-강남대 / 컴퓨터학과 / 학점 2.89 / 토익스피킹: 110/5, 오픽: IL / 기타: 정보처리기사
-자소서 작성
-보고있는 합격자소서 참고해서 내 자소서 작성하기
-스크랩하기
-공유하기
-새창
-목록
-마음에 드는 문장을 스크랩 할 수 있어요!
-최고 품질의 상품들을 지금보다 더 많은 소비자들이 여러 유통 채널에서 더욱 폭 넓고 쉽게...
-다시보지 않기
-[클린코드 - 올바른 코딩을 위한 노력]
+          <t>[클린코드 - 올바른 코딩을 위한 노력]
 개발자 동료들에게 추천하고 싶은 책은 저자 로버트 마틴의 '클린코드'라는 책입니다. 이 책에서는 나쁜 코드로 인해 어려움을 겪은 로버트 마틴이 수 십 년의 경험을 통해 클린한 코드가 무엇인지, 어떻게 구현해야 하는지에 대해서 설명하고 있습니다. 특출난 프로그래머가 생각하는 방식과 그들이 사용하는 기술과 기교, 도구 등을 소개하고 있습니다.
 이 책에서 TDD(Test Driven Development)에 대한 이야기를 알게 되었습니다. TDD의 특성은 1- 실패하는 단위 테스트를 작성할 때까지 실제 코드를 작성하지 않는다. 2-컴파일은 실패하지 않으면서 실행이 실패하는 정도로만 단위테스트를 작성한다. 3- 현재 실패하는 테스트를 통과할 정도로 실제 코드를 작성한다. 입니다. 이 세가지 규칙에 의해 개발하는 방법이 TDD인 것입니다. 테스트 코드가 실제 코드보다 몇초 전에 나오게 됩니다. 테스트 코드를 작성하고 테스트 코드를 통과할 수 있는 코드를 작성하는 방식입니다. 이 방식은 코드의 유연성, 유지보수성, 재사용성을 제공합니다. 테스트 케이스가 있으면 코드 변경 또한 가능하기 때문입니다. 테스트 케이스가 없다면 모든 변경이 잠정적 버그지만, 테스트 케이스가 존재한다면 테스트 케이스에 어긋나지 않는 코드를 작성하기만 하면 되기 때문입니다. 아무리 아키텍처가 훌륭하고, 좋은 설계라 할지라도 테스트 케이스가 없다면 그 코드는 잠정적인 버그를 일으킬 수 있습니다. 그렇기 때문에 TDD가 필요한 것입니다.
 이 외에도 설계규칙에 대한 이야기, 클래스에 대한 설명 등 여러 정보를 포함하고 있습니다. 저 또한 이 책을 추천받아 읽게 되었습니다. 추천 사유는 개발은 개발량에 비례해 실력이 느는 것이아니라는 이유때문이었습니다. 이 책을 읽고 난 후 그 말의 의미에 대해 알게 되었습니다. 다양한 개발방식에서 제가 효율적이라고 생각한 방식, 즉 구현에 집중해서 빨리 코딩하는 방식만을 사용했었습니다. 이 책을 통해 개발자로서 발전할 방향과 가능성을 느꼈고, 개발자 동료들에게 이 책을 추천하고 싶습니다.
@@ -4406,9 +4058,7 @@
 자주 갔던 위메프 카페를 이용하기 위해 위메프오 앱을 처음 사용했습니다. 앱을 사용함으로써 메뉴의 가격을 미리 볼 수 있고 주문결제 시스템의 단순화가 가장 큰 장점이었습니다. 픽업서비스를 이용해 시간의 단축 뿐 아니라 주문하기 위해 줄을 서있어야 할 필요도 줄었기 때문이었습니다. 
 개발자로서 위메프오의 장점은 내 위치 기반으로 가까운 지점을 우선으로 보여주기에 이용하기 참 편리했습니다. UI 측면에서도 자주가는 카페가 가장 먼저 보이는 부분이 가장 좋았습니다. 주로 한 군데 지점을 이용했기에 여러 페이지를 거치지 않고 직관적으로 UI가 구성되있다고 느꼈습니다. 결제 시스템 또한 처음 등록 이후 원터치 결제 방식으로 느낄만큼 편리하게 이용했습니다.
 단점으로는 앱에 들어가게되면 배달/픽업 부분과 할인티켓 부분이 나눠져 있었습니다. 두개의 독립적인 서비스가 한 어플에서 제공되는 것이 소비자 입장에서 유쾌하지 않은 경험이었단 생각이 들었습니다. 제가 만약 서비스를 하게 되었다면 위메프오 서비스를 위메프오배달/픽업 앱과 위메프오티켓 앱으로 나눌 것 같습니다. 위메프오는 O2O라는 의미에서 지은 개념으로 알고있습니다. 그래서 위메프오는 상징적으로 놔두고 앞으로 새롭게 출시될 어플을 계속적으로 추가하면 확장성 측면에서도 좋을 것입니다.
- 위메프오 배달,픽업 서비스에서 제가 적용하고 싶은 서비스는 추천 시스템입니다. 대부분 사용자는 본인이 맛있다고 생각한 음식을 단골집으로 지정해 자주 사용할 것입니다. 이러한 정보를 바탕으로 넷플릭스가 영화 추천을 위해 사용하는 Matrix Factorization 알고리즘을 사용하고 싶습니다. 유저의 특징과 음식점의 특징에 대해 학습하여 유저가 좋아할만한 음식점을 추천하는 것입니다. 그런 경우, 유저는 기존에 선호하던 음식과 비슷한 음식을 추천받을 수 있고, 위메프는 다양한 식당을 유저에게 제공함으로써 오는 수익을 얻을 수 있을 것이라 생각합니다.
-새창
-목록</t>
+ 위메프오 배달,픽업 서비스에서 제가 적용하고 싶은 서비스는 추천 시스템입니다. 대부분 사용자는 본인이 맛있다고 생각한 음식을 단골집으로 지정해 자주 사용할 것입니다. 이러한 정보를 바탕으로 넷플릭스가 영화 추천을 위해 사용하는 Matrix Factorization 알고리즘을 사용하고 싶습니다. 유저의 특징과 음식점의 특징에 대해 학습하여 유저가 좋아할만한 음식점을 추천하는 것입니다. 그런 경우, 유저는 기존에 선호하던 음식과 비슷한 음식을 추천받을 수 있고, 위메프는 다양한 식당을 유저에게 제공함으로써 오는 수익을 얻을 수 있을 것이라 생각합니다.</t>
         </is>
       </c>
     </row>
